--- a/output/roomself_excel/6578.xlsx
+++ b/output/roomself_excel/6578.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>342656</v>
+        <v>140696</v>
       </c>
       <c r="D2" t="n">
-        <v>6384</v>
+        <v>3132</v>
       </c>
       <c r="E2" t="n">
-        <v>896</v>
+        <v>493</v>
       </c>
       <c r="F2" t="n">
-        <v>746</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>56797</v>
+        <v>201960</v>
       </c>
       <c r="D3" t="n">
-        <v>2288</v>
+        <v>3684</v>
       </c>
       <c r="E3" t="n">
-        <v>197</v>
+        <v>600</v>
       </c>
       <c r="F3" t="n">
-        <v>126</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35574</v>
+        <v>163512</v>
       </c>
       <c r="D4" t="n">
-        <v>1540</v>
+        <v>3316</v>
       </c>
       <c r="E4" t="n">
-        <v>247</v>
+        <v>495</v>
       </c>
       <c r="F4" t="n">
-        <v>170</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>163512</v>
+        <v>56797</v>
       </c>
       <c r="D5" t="n">
-        <v>3316</v>
+        <v>2288</v>
       </c>
       <c r="E5" t="n">
-        <v>565</v>
+        <v>126</v>
       </c>
       <c r="F5" t="n">
-        <v>495</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -558,15 +558,37 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>35574</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1540</v>
+      </c>
+      <c r="E6" t="n">
+        <v>247</v>
+      </c>
+      <c r="F6" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>29190</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>1396</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>236</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>155</v>
       </c>
     </row>

--- a/output/roomself_excel/6578.xlsx
+++ b/output/roomself_excel/6578.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3132</v>
       </c>
-      <c r="E2" t="n">
-        <v>493</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>330</v>
+        <v>314</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>396</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3684</v>
       </c>
-      <c r="E3" t="n">
-        <v>600</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>401</v>
+        <v>561</v>
+      </c>
+      <c r="G3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>359</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>3316</v>
       </c>
-      <c r="E4" t="n">
-        <v>495</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>395</v>
+        <v>469</v>
+      </c>
+      <c r="G4" t="n">
+        <v>41</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>354</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +609,20 @@
       <c r="D5" t="n">
         <v>2288</v>
       </c>
-      <c r="E5" t="n">
-        <v>126</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +639,27 @@
       <c r="D6" t="n">
         <v>1540</v>
       </c>
-      <c r="E6" t="n">
-        <v>247</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>170</v>
+        <v>231</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>154</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -585,11 +677,27 @@
       <c r="D7" t="n">
         <v>1396</v>
       </c>
-      <c r="E7" t="n">
-        <v>236</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>155</v>
+        <v>210</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>139</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/6578.xlsx
+++ b/output/roomself_excel/6578.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +557,26 @@
       <c r="J2" t="n">
         <v>16</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>208</v>
+      </c>
+      <c r="N2" t="n">
+        <v>39</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,6 +615,38 @@
       <c r="J3" t="n">
         <v>39</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>211</v>
+      </c>
+      <c r="N3" t="n">
+        <v>39</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>86</v>
+      </c>
+      <c r="R3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -593,6 +685,26 @@
       <c r="J4" t="n">
         <v>26</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>214</v>
+      </c>
+      <c r="N4" t="n">
+        <v>26</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -623,6 +735,14 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -661,6 +781,14 @@
       <c r="J6" t="n">
         <v>16</v>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -699,6 +827,26 @@
       <c r="J7" t="n">
         <v>26</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>94</v>
+      </c>
+      <c r="N7" t="n">
+        <v>26</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
